--- a/quizzes/034_laboratory_management_trends_quiz--quizzes.xlsx
+++ b/quizzes/034_laboratory_management_trends_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,15 +520,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>laboratory_management_roles</t>
+          <t>current_laboratory_roles</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>laboratory_management_roles</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Current Laboratory Roles</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Describe the current state of laboratory roles in your hospital</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -548,10 +552,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>key_trends</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Key Trends in Laboratory Management</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Describe the key trends in your laboratory management</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -571,10 +579,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>challenges</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Challenges in Laboratory Management</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Describe the current challenges in your laboratory management</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -594,10 +606,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>technology_adoption</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Hospital Technology Adoption</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Rate your hospital's technology adoption in the laboratory</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -607,20 +623,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>technology_adoption_rate</t>
+          <t>hospital_size</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>technology_adoption_rate</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Hospital Size</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Describe your hospital's size</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -630,20 +650,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>laboratory_management_trends</t>
+          <t>hospital_type</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>laboratory_management_trends</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Hospital Type</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Describe the type of hospital you work in</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -653,20 +677,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>roles</t>
+          <t>hospital_tier</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>roles</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Hospital Tier</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Describe the hospital's tier</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -676,20 +704,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>hospital_department</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>hospital</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Hospital Department</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Describe the department you work in</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -699,20 +731,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hospital_size</t>
+          <t>technology_adoption_description</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>hospital_size</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Technology Adoption Description</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Describe your hospital's technology adoption in the laboratory</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -722,20 +758,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hospital_type</t>
+          <t>challenges_description</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>hospital_type</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Challenges Description</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Describe the current challenges in your laboratory management</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -745,20 +785,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hospital_tier</t>
+          <t>laboratory_management_trends</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>hospital_tier</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Laboratory Management Trends</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Describe the current trends in your laboratory management</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -768,20 +812,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>hospital_department</t>
+          <t>hospital_name</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>hospital_department</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Hospital Name</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please specify your hospital's name</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -801,10 +849,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>roles_description</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Roles Description</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Describe the current state of laboratory roles</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -819,15 +871,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>technology_adoption_description</t>
+          <t>key_trends_description</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>technology_adoption_description</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Key Trends Description</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Describe the current key trends in laboratory management</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -842,15 +898,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>challenges_description</t>
+          <t>hospital_size_description</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>challenges_description</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Hospital Size Description</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Describe the size of your hospital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -865,15 +925,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>laboratory_management_trends_description</t>
+          <t>hospital_type_description</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>laboratory_management_trends_description</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Hospital Type Description</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Describe the type of hospital you work in</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -888,200 +952,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>hospital_tier_description</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>hospital</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Hospital Tier Description</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Describe the hospital's tier</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>hospital_size</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>hospital_size</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>hospital_type</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>hospital_type</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>hospital_tier</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>hospital_tier</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>laboratory_management_roles</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>laboratory_management_roles</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>key_trends</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>key_trends</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>roles</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>roles</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>laboratory_management_trends</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>laboratory_management_trends</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>hospital</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>hospital</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +982,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,75 +1010,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>laboratory_management_roles_choices</t>
+          <t>current_laboratory_roles_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>clinical_laboratory</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Clinical Laboratory</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>laboratory_management_roles_choices</t>
+          <t>current_laboratory_roles_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>research_laboratory</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Research Laboratory</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>technology_adoption_choices</t>
+          <t>current_laboratory_roles_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>testing_and_validation_laboratory</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Testing and Validation Laboratory</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>technology_adoption_choices</t>
+          <t>current_laboratory_roles_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other (Please Specify)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>roles_choices</t>
+          <t>technology_adoption_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +1095,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>roles_choices</t>
+          <t>technology_adoption_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,34 +1112,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>hospital_choices</t>
+          <t>hospital_size_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>hospital_choices</t>
+          <t>hospital_size_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1267,29 +1151,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>hospital_size_choices</t>
+          <t>hospital_type_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>academic</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Academic</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1185,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>teaching</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Teaching</t>
         </is>
       </c>
     </row>
@@ -1318,29 +1202,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>research</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Research</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>hospital_tier_choices</t>
+          <t>hospital_type_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>community</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Community</t>
         </is>
       </c>
     </row>
@@ -1352,46 +1236,114 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>tier_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Tier 1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>hospital_department_choices</t>
+          <t>hospital_tier_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>tier_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Tier 2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>hospital_tier_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>tier_3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>hospital_department_choices</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>clinical_laboratory</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Clinical Laboratory</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>hospital_department_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>research_laboratory</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Research Laboratory</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>hospital_department_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>testing_and_validation_laboratory</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Testing and Validation Laboratory</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>hospital_department_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Other (Please Specify)</t>
         </is>
       </c>
     </row>
